--- a/assetcore/public/import_templates/02_imm00_ncc_model_hopdong_sla.xlsx
+++ b/assetcore/public/import_templates/02_imm00_ncc_model_hopdong_sla.xlsx
@@ -2953,7 +2953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V105"/>
+  <dimension ref="A1:U105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2965,19 +2965,18 @@
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="35" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="26" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="28" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="26" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="40" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="28" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="40" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -3035,65 +3034,60 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>emdn_code</t>
+          <t>registration_required</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>registration_required</t>
+          <t>is_radiation_device</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>is_radiation_device</t>
+          <t>is_pm_required</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>is_pm_required</t>
+          <t>pm_interval_days</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>pm_interval_days</t>
+          <t>pm_alert_days</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>pm_alert_days</t>
+          <t>is_calibration_required</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>is_calibration_required</t>
+          <t>calibration_interval_days</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>calibration_interval_days</t>
+          <t>default_calibration_type</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>default_calibration_type</t>
+          <t>power_supply</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>power_supply</t>
+          <t>dimensions</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>dimensions</t>
+          <t>weight_kg</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>weight_kg</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>specifications</t>
         </is>
@@ -3147,65 +3141,60 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Mã EMDN</t>
+          <t>Cần số đăng ký BYT?</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>Cần số đăng ký BYT?</t>
+          <t>Thiết bị bức xạ?</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>Thiết bị bức xạ?</t>
+          <t>Cần bảo trì ĐK?</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>Cần bảo trì ĐK?</t>
+          <t>Chu kỳ PM (ngày)</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
         <is>
-          <t>Chu kỳ PM (ngày)</t>
+          <t>Cảnh báo PM trước (ngày)</t>
         </is>
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
-          <t>Cảnh báo PM trước (ngày)</t>
+          <t>Cần hiệu chuẩn?</t>
         </is>
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>Cần hiệu chuẩn?</t>
+          <t>Chu kỳ hiệu chuẩn (ngày)</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>Chu kỳ hiệu chuẩn (ngày)</t>
+          <t>Loại hiệu chuẩn</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>Loại hiệu chuẩn</t>
+          <t>Nguồn điện</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>Nguồn điện</t>
+          <t>Kích thước (DxRxC, mm)</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>Kích thước (DxRxC, mm)</t>
+          <t>Trọng lượng (kg)</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
-        <is>
-          <t>Trọng lượng (kg)</t>
-        </is>
-      </c>
-      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>Thông số kỹ thuật</t>
         </is>
@@ -3259,65 +3248,60 @@
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>Mã EMDN (châu Âu, nếu có).</t>
+          <t>1 = bắt buộc có số ĐKLH Bộ Y tế; 0 = không.</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>1 = bắt buộc có số ĐKLH Bộ Y tế; 0 = không.</t>
+          <t>1 = có phát xạ ion hóa (X-quang, CT...); 0 = không.</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>1 = có phát xạ ion hóa (X-quang, CT...); 0 = không.</t>
+          <t>1 = có lịch PM; 0 = không.</t>
         </is>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>1 = có lịch PM; 0 = không.</t>
+          <t>Số ngày giữa 2 lần bảo trì. Bắt buộc nếu PM = 1.</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>Số ngày giữa 2 lần bảo trì. Bắt buộc nếu PM = 1.</t>
+          <t>Số ngày cảnh báo trước khi đến hạn PM. Mặc định: 30.</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>Số ngày cảnh báo trước khi đến hạn PM. Mặc định: 30.</t>
+          <t>1 = có lịch hiệu chuẩn; 0 = không.</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>1 = có lịch hiệu chuẩn; 0 = không.</t>
+          <t>Số ngày giữa 2 lần hiệu chuẩn. Bắt buộc nếu HC = 1.</t>
         </is>
       </c>
       <c r="Q4" s="6" t="inlineStr">
         <is>
-          <t>Số ngày giữa 2 lần hiệu chuẩn. Bắt buộc nếu HC = 1.</t>
+          <t>Internal / External / Both</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>Internal / External / Both</t>
+          <t>VD: 220V/50Hz, 110-240V/50-60Hz.</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
         <is>
-          <t>VD: 220V/50Hz, 110-240V/50-60Hz.</t>
+          <t>Dài x Rộng x Cao, đơn vị mm.</t>
         </is>
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
-          <t>Dài x Rộng x Cao, đơn vị mm.</t>
+          <t>Trọng lượng máy (kg).</t>
         </is>
       </c>
       <c r="U4" s="6" t="inlineStr">
-        <is>
-          <t>Trọng lượng máy (kg).</t>
-        </is>
-      </c>
-      <c r="V4" s="6" t="inlineStr">
         <is>
           <t>Mô tả thông số kỹ thuật chính.</t>
         </is>
@@ -3371,65 +3355,60 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>Z12.060.030</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="O5" s="7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>365</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>External</t>
         </is>
       </c>
       <c r="R5" s="7" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>220V/50Hz</t>
         </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>220V/50Hz</t>
+          <t>600x800x1200</t>
         </is>
       </c>
       <c r="T5" s="7" t="inlineStr">
         <is>
-          <t>600x800x1200</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>85.5</t>
-        </is>
-      </c>
-      <c r="V5" s="7" t="inlineStr">
         <is>
           <t>Frequency: 1-18 MHz; 4 probe ports</t>
         </is>
@@ -3457,7 +3436,6 @@
       <c r="S6" s="8" t="n"/>
       <c r="T6" s="8" t="n"/>
       <c r="U6" s="8" t="n"/>
-      <c r="V6" s="8" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="9" t="n"/>
@@ -3481,7 +3459,6 @@
       <c r="S7" s="9" t="n"/>
       <c r="T7" s="9" t="n"/>
       <c r="U7" s="9" t="n"/>
-      <c r="V7" s="9" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="8" t="n"/>
@@ -3505,7 +3482,6 @@
       <c r="S8" s="8" t="n"/>
       <c r="T8" s="8" t="n"/>
       <c r="U8" s="8" t="n"/>
-      <c r="V8" s="8" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="9" t="n"/>
@@ -3529,7 +3505,6 @@
       <c r="S9" s="9" t="n"/>
       <c r="T9" s="9" t="n"/>
       <c r="U9" s="9" t="n"/>
-      <c r="V9" s="9" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="8" t="n"/>
@@ -3553,7 +3528,6 @@
       <c r="S10" s="8" t="n"/>
       <c r="T10" s="8" t="n"/>
       <c r="U10" s="8" t="n"/>
-      <c r="V10" s="8" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="9" t="n"/>
@@ -3577,7 +3551,6 @@
       <c r="S11" s="9" t="n"/>
       <c r="T11" s="9" t="n"/>
       <c r="U11" s="9" t="n"/>
-      <c r="V11" s="9" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="8" t="n"/>
@@ -3601,7 +3574,6 @@
       <c r="S12" s="8" t="n"/>
       <c r="T12" s="8" t="n"/>
       <c r="U12" s="8" t="n"/>
-      <c r="V12" s="8" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="9" t="n"/>
@@ -3625,7 +3597,6 @@
       <c r="S13" s="9" t="n"/>
       <c r="T13" s="9" t="n"/>
       <c r="U13" s="9" t="n"/>
-      <c r="V13" s="9" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="8" t="n"/>
@@ -3649,7 +3620,6 @@
       <c r="S14" s="8" t="n"/>
       <c r="T14" s="8" t="n"/>
       <c r="U14" s="8" t="n"/>
-      <c r="V14" s="8" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="9" t="n"/>
@@ -3673,7 +3643,6 @@
       <c r="S15" s="9" t="n"/>
       <c r="T15" s="9" t="n"/>
       <c r="U15" s="9" t="n"/>
-      <c r="V15" s="9" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="8" t="n"/>
@@ -3697,7 +3666,6 @@
       <c r="S16" s="8" t="n"/>
       <c r="T16" s="8" t="n"/>
       <c r="U16" s="8" t="n"/>
-      <c r="V16" s="8" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="9" t="n"/>
@@ -3721,7 +3689,6 @@
       <c r="S17" s="9" t="n"/>
       <c r="T17" s="9" t="n"/>
       <c r="U17" s="9" t="n"/>
-      <c r="V17" s="9" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="8" t="n"/>
@@ -3745,7 +3712,6 @@
       <c r="S18" s="8" t="n"/>
       <c r="T18" s="8" t="n"/>
       <c r="U18" s="8" t="n"/>
-      <c r="V18" s="8" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="9" t="n"/>
@@ -3769,7 +3735,6 @@
       <c r="S19" s="9" t="n"/>
       <c r="T19" s="9" t="n"/>
       <c r="U19" s="9" t="n"/>
-      <c r="V19" s="9" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="8" t="n"/>
@@ -3793,7 +3758,6 @@
       <c r="S20" s="8" t="n"/>
       <c r="T20" s="8" t="n"/>
       <c r="U20" s="8" t="n"/>
-      <c r="V20" s="8" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="9" t="n"/>
@@ -3817,7 +3781,6 @@
       <c r="S21" s="9" t="n"/>
       <c r="T21" s="9" t="n"/>
       <c r="U21" s="9" t="n"/>
-      <c r="V21" s="9" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="8" t="n"/>
@@ -3841,7 +3804,6 @@
       <c r="S22" s="8" t="n"/>
       <c r="T22" s="8" t="n"/>
       <c r="U22" s="8" t="n"/>
-      <c r="V22" s="8" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="9" t="n"/>
@@ -3865,7 +3827,6 @@
       <c r="S23" s="9" t="n"/>
       <c r="T23" s="9" t="n"/>
       <c r="U23" s="9" t="n"/>
-      <c r="V23" s="9" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="8" t="n"/>
@@ -3889,7 +3850,6 @@
       <c r="S24" s="8" t="n"/>
       <c r="T24" s="8" t="n"/>
       <c r="U24" s="8" t="n"/>
-      <c r="V24" s="8" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="9" t="n"/>
@@ -3913,7 +3873,6 @@
       <c r="S25" s="9" t="n"/>
       <c r="T25" s="9" t="n"/>
       <c r="U25" s="9" t="n"/>
-      <c r="V25" s="9" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="8" t="n"/>
@@ -3937,7 +3896,6 @@
       <c r="S26" s="8" t="n"/>
       <c r="T26" s="8" t="n"/>
       <c r="U26" s="8" t="n"/>
-      <c r="V26" s="8" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="9" t="n"/>
@@ -3961,7 +3919,6 @@
       <c r="S27" s="9" t="n"/>
       <c r="T27" s="9" t="n"/>
       <c r="U27" s="9" t="n"/>
-      <c r="V27" s="9" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="8" t="n"/>
@@ -3985,7 +3942,6 @@
       <c r="S28" s="8" t="n"/>
       <c r="T28" s="8" t="n"/>
       <c r="U28" s="8" t="n"/>
-      <c r="V28" s="8" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="9" t="n"/>
@@ -4009,7 +3965,6 @@
       <c r="S29" s="9" t="n"/>
       <c r="T29" s="9" t="n"/>
       <c r="U29" s="9" t="n"/>
-      <c r="V29" s="9" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="8" t="n"/>
@@ -4033,7 +3988,6 @@
       <c r="S30" s="8" t="n"/>
       <c r="T30" s="8" t="n"/>
       <c r="U30" s="8" t="n"/>
-      <c r="V30" s="8" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="9" t="n"/>
@@ -4057,7 +4011,6 @@
       <c r="S31" s="9" t="n"/>
       <c r="T31" s="9" t="n"/>
       <c r="U31" s="9" t="n"/>
-      <c r="V31" s="9" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="8" t="n"/>
@@ -4081,7 +4034,6 @@
       <c r="S32" s="8" t="n"/>
       <c r="T32" s="8" t="n"/>
       <c r="U32" s="8" t="n"/>
-      <c r="V32" s="8" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="9" t="n"/>
@@ -4105,7 +4057,6 @@
       <c r="S33" s="9" t="n"/>
       <c r="T33" s="9" t="n"/>
       <c r="U33" s="9" t="n"/>
-      <c r="V33" s="9" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="8" t="n"/>
@@ -4129,7 +4080,6 @@
       <c r="S34" s="8" t="n"/>
       <c r="T34" s="8" t="n"/>
       <c r="U34" s="8" t="n"/>
-      <c r="V34" s="8" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="9" t="n"/>
@@ -4153,7 +4103,6 @@
       <c r="S35" s="9" t="n"/>
       <c r="T35" s="9" t="n"/>
       <c r="U35" s="9" t="n"/>
-      <c r="V35" s="9" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="8" t="n"/>
@@ -4177,7 +4126,6 @@
       <c r="S36" s="8" t="n"/>
       <c r="T36" s="8" t="n"/>
       <c r="U36" s="8" t="n"/>
-      <c r="V36" s="8" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="9" t="n"/>
@@ -4201,7 +4149,6 @@
       <c r="S37" s="9" t="n"/>
       <c r="T37" s="9" t="n"/>
       <c r="U37" s="9" t="n"/>
-      <c r="V37" s="9" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="8" t="n"/>
@@ -4225,7 +4172,6 @@
       <c r="S38" s="8" t="n"/>
       <c r="T38" s="8" t="n"/>
       <c r="U38" s="8" t="n"/>
-      <c r="V38" s="8" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="9" t="n"/>
@@ -4249,7 +4195,6 @@
       <c r="S39" s="9" t="n"/>
       <c r="T39" s="9" t="n"/>
       <c r="U39" s="9" t="n"/>
-      <c r="V39" s="9" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="8" t="n"/>
@@ -4273,7 +4218,6 @@
       <c r="S40" s="8" t="n"/>
       <c r="T40" s="8" t="n"/>
       <c r="U40" s="8" t="n"/>
-      <c r="V40" s="8" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="9" t="n"/>
@@ -4297,7 +4241,6 @@
       <c r="S41" s="9" t="n"/>
       <c r="T41" s="9" t="n"/>
       <c r="U41" s="9" t="n"/>
-      <c r="V41" s="9" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="8" t="n"/>
@@ -4321,7 +4264,6 @@
       <c r="S42" s="8" t="n"/>
       <c r="T42" s="8" t="n"/>
       <c r="U42" s="8" t="n"/>
-      <c r="V42" s="8" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="9" t="n"/>
@@ -4345,7 +4287,6 @@
       <c r="S43" s="9" t="n"/>
       <c r="T43" s="9" t="n"/>
       <c r="U43" s="9" t="n"/>
-      <c r="V43" s="9" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="8" t="n"/>
@@ -4369,7 +4310,6 @@
       <c r="S44" s="8" t="n"/>
       <c r="T44" s="8" t="n"/>
       <c r="U44" s="8" t="n"/>
-      <c r="V44" s="8" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="9" t="n"/>
@@ -4393,7 +4333,6 @@
       <c r="S45" s="9" t="n"/>
       <c r="T45" s="9" t="n"/>
       <c r="U45" s="9" t="n"/>
-      <c r="V45" s="9" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="8" t="n"/>
@@ -4417,7 +4356,6 @@
       <c r="S46" s="8" t="n"/>
       <c r="T46" s="8" t="n"/>
       <c r="U46" s="8" t="n"/>
-      <c r="V46" s="8" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="9" t="n"/>
@@ -4441,7 +4379,6 @@
       <c r="S47" s="9" t="n"/>
       <c r="T47" s="9" t="n"/>
       <c r="U47" s="9" t="n"/>
-      <c r="V47" s="9" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="8" t="n"/>
@@ -4465,7 +4402,6 @@
       <c r="S48" s="8" t="n"/>
       <c r="T48" s="8" t="n"/>
       <c r="U48" s="8" t="n"/>
-      <c r="V48" s="8" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="9" t="n"/>
@@ -4489,7 +4425,6 @@
       <c r="S49" s="9" t="n"/>
       <c r="T49" s="9" t="n"/>
       <c r="U49" s="9" t="n"/>
-      <c r="V49" s="9" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="8" t="n"/>
@@ -4513,7 +4448,6 @@
       <c r="S50" s="8" t="n"/>
       <c r="T50" s="8" t="n"/>
       <c r="U50" s="8" t="n"/>
-      <c r="V50" s="8" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="9" t="n"/>
@@ -4537,7 +4471,6 @@
       <c r="S51" s="9" t="n"/>
       <c r="T51" s="9" t="n"/>
       <c r="U51" s="9" t="n"/>
-      <c r="V51" s="9" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="8" t="n"/>
@@ -4561,7 +4494,6 @@
       <c r="S52" s="8" t="n"/>
       <c r="T52" s="8" t="n"/>
       <c r="U52" s="8" t="n"/>
-      <c r="V52" s="8" t="n"/>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="9" t="n"/>
@@ -4585,7 +4517,6 @@
       <c r="S53" s="9" t="n"/>
       <c r="T53" s="9" t="n"/>
       <c r="U53" s="9" t="n"/>
-      <c r="V53" s="9" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="8" t="n"/>
@@ -4609,7 +4540,6 @@
       <c r="S54" s="8" t="n"/>
       <c r="T54" s="8" t="n"/>
       <c r="U54" s="8" t="n"/>
-      <c r="V54" s="8" t="n"/>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="9" t="n"/>
@@ -4633,7 +4563,6 @@
       <c r="S55" s="9" t="n"/>
       <c r="T55" s="9" t="n"/>
       <c r="U55" s="9" t="n"/>
-      <c r="V55" s="9" t="n"/>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="8" t="n"/>
@@ -4657,7 +4586,6 @@
       <c r="S56" s="8" t="n"/>
       <c r="T56" s="8" t="n"/>
       <c r="U56" s="8" t="n"/>
-      <c r="V56" s="8" t="n"/>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="9" t="n"/>
@@ -4681,7 +4609,6 @@
       <c r="S57" s="9" t="n"/>
       <c r="T57" s="9" t="n"/>
       <c r="U57" s="9" t="n"/>
-      <c r="V57" s="9" t="n"/>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="8" t="n"/>
@@ -4705,7 +4632,6 @@
       <c r="S58" s="8" t="n"/>
       <c r="T58" s="8" t="n"/>
       <c r="U58" s="8" t="n"/>
-      <c r="V58" s="8" t="n"/>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="9" t="n"/>
@@ -4729,7 +4655,6 @@
       <c r="S59" s="9" t="n"/>
       <c r="T59" s="9" t="n"/>
       <c r="U59" s="9" t="n"/>
-      <c r="V59" s="9" t="n"/>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="8" t="n"/>
@@ -4753,7 +4678,6 @@
       <c r="S60" s="8" t="n"/>
       <c r="T60" s="8" t="n"/>
       <c r="U60" s="8" t="n"/>
-      <c r="V60" s="8" t="n"/>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="9" t="n"/>
@@ -4777,7 +4701,6 @@
       <c r="S61" s="9" t="n"/>
       <c r="T61" s="9" t="n"/>
       <c r="U61" s="9" t="n"/>
-      <c r="V61" s="9" t="n"/>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="8" t="n"/>
@@ -4801,7 +4724,6 @@
       <c r="S62" s="8" t="n"/>
       <c r="T62" s="8" t="n"/>
       <c r="U62" s="8" t="n"/>
-      <c r="V62" s="8" t="n"/>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="9" t="n"/>
@@ -4825,7 +4747,6 @@
       <c r="S63" s="9" t="n"/>
       <c r="T63" s="9" t="n"/>
       <c r="U63" s="9" t="n"/>
-      <c r="V63" s="9" t="n"/>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="8" t="n"/>
@@ -4849,7 +4770,6 @@
       <c r="S64" s="8" t="n"/>
       <c r="T64" s="8" t="n"/>
       <c r="U64" s="8" t="n"/>
-      <c r="V64" s="8" t="n"/>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="9" t="n"/>
@@ -4873,7 +4793,6 @@
       <c r="S65" s="9" t="n"/>
       <c r="T65" s="9" t="n"/>
       <c r="U65" s="9" t="n"/>
-      <c r="V65" s="9" t="n"/>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="8" t="n"/>
@@ -4897,7 +4816,6 @@
       <c r="S66" s="8" t="n"/>
       <c r="T66" s="8" t="n"/>
       <c r="U66" s="8" t="n"/>
-      <c r="V66" s="8" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="9" t="n"/>
@@ -4921,7 +4839,6 @@
       <c r="S67" s="9" t="n"/>
       <c r="T67" s="9" t="n"/>
       <c r="U67" s="9" t="n"/>
-      <c r="V67" s="9" t="n"/>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="8" t="n"/>
@@ -4945,7 +4862,6 @@
       <c r="S68" s="8" t="n"/>
       <c r="T68" s="8" t="n"/>
       <c r="U68" s="8" t="n"/>
-      <c r="V68" s="8" t="n"/>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="9" t="n"/>
@@ -4969,7 +4885,6 @@
       <c r="S69" s="9" t="n"/>
       <c r="T69" s="9" t="n"/>
       <c r="U69" s="9" t="n"/>
-      <c r="V69" s="9" t="n"/>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="8" t="n"/>
@@ -4993,7 +4908,6 @@
       <c r="S70" s="8" t="n"/>
       <c r="T70" s="8" t="n"/>
       <c r="U70" s="8" t="n"/>
-      <c r="V70" s="8" t="n"/>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="9" t="n"/>
@@ -5017,7 +4931,6 @@
       <c r="S71" s="9" t="n"/>
       <c r="T71" s="9" t="n"/>
       <c r="U71" s="9" t="n"/>
-      <c r="V71" s="9" t="n"/>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="8" t="n"/>
@@ -5041,7 +4954,6 @@
       <c r="S72" s="8" t="n"/>
       <c r="T72" s="8" t="n"/>
       <c r="U72" s="8" t="n"/>
-      <c r="V72" s="8" t="n"/>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="9" t="n"/>
@@ -5065,7 +4977,6 @@
       <c r="S73" s="9" t="n"/>
       <c r="T73" s="9" t="n"/>
       <c r="U73" s="9" t="n"/>
-      <c r="V73" s="9" t="n"/>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="8" t="n"/>
@@ -5089,7 +5000,6 @@
       <c r="S74" s="8" t="n"/>
       <c r="T74" s="8" t="n"/>
       <c r="U74" s="8" t="n"/>
-      <c r="V74" s="8" t="n"/>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="9" t="n"/>
@@ -5113,7 +5023,6 @@
       <c r="S75" s="9" t="n"/>
       <c r="T75" s="9" t="n"/>
       <c r="U75" s="9" t="n"/>
-      <c r="V75" s="9" t="n"/>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="8" t="n"/>
@@ -5137,7 +5046,6 @@
       <c r="S76" s="8" t="n"/>
       <c r="T76" s="8" t="n"/>
       <c r="U76" s="8" t="n"/>
-      <c r="V76" s="8" t="n"/>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="9" t="n"/>
@@ -5161,7 +5069,6 @@
       <c r="S77" s="9" t="n"/>
       <c r="T77" s="9" t="n"/>
       <c r="U77" s="9" t="n"/>
-      <c r="V77" s="9" t="n"/>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="8" t="n"/>
@@ -5185,7 +5092,6 @@
       <c r="S78" s="8" t="n"/>
       <c r="T78" s="8" t="n"/>
       <c r="U78" s="8" t="n"/>
-      <c r="V78" s="8" t="n"/>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="9" t="n"/>
@@ -5209,7 +5115,6 @@
       <c r="S79" s="9" t="n"/>
       <c r="T79" s="9" t="n"/>
       <c r="U79" s="9" t="n"/>
-      <c r="V79" s="9" t="n"/>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="8" t="n"/>
@@ -5233,7 +5138,6 @@
       <c r="S80" s="8" t="n"/>
       <c r="T80" s="8" t="n"/>
       <c r="U80" s="8" t="n"/>
-      <c r="V80" s="8" t="n"/>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="9" t="n"/>
@@ -5257,7 +5161,6 @@
       <c r="S81" s="9" t="n"/>
       <c r="T81" s="9" t="n"/>
       <c r="U81" s="9" t="n"/>
-      <c r="V81" s="9" t="n"/>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="8" t="n"/>
@@ -5281,7 +5184,6 @@
       <c r="S82" s="8" t="n"/>
       <c r="T82" s="8" t="n"/>
       <c r="U82" s="8" t="n"/>
-      <c r="V82" s="8" t="n"/>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="9" t="n"/>
@@ -5305,7 +5207,6 @@
       <c r="S83" s="9" t="n"/>
       <c r="T83" s="9" t="n"/>
       <c r="U83" s="9" t="n"/>
-      <c r="V83" s="9" t="n"/>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="8" t="n"/>
@@ -5329,7 +5230,6 @@
       <c r="S84" s="8" t="n"/>
       <c r="T84" s="8" t="n"/>
       <c r="U84" s="8" t="n"/>
-      <c r="V84" s="8" t="n"/>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="9" t="n"/>
@@ -5353,7 +5253,6 @@
       <c r="S85" s="9" t="n"/>
       <c r="T85" s="9" t="n"/>
       <c r="U85" s="9" t="n"/>
-      <c r="V85" s="9" t="n"/>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="8" t="n"/>
@@ -5377,7 +5276,6 @@
       <c r="S86" s="8" t="n"/>
       <c r="T86" s="8" t="n"/>
       <c r="U86" s="8" t="n"/>
-      <c r="V86" s="8" t="n"/>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="9" t="n"/>
@@ -5401,7 +5299,6 @@
       <c r="S87" s="9" t="n"/>
       <c r="T87" s="9" t="n"/>
       <c r="U87" s="9" t="n"/>
-      <c r="V87" s="9" t="n"/>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="8" t="n"/>
@@ -5425,7 +5322,6 @@
       <c r="S88" s="8" t="n"/>
       <c r="T88" s="8" t="n"/>
       <c r="U88" s="8" t="n"/>
-      <c r="V88" s="8" t="n"/>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="9" t="n"/>
@@ -5449,7 +5345,6 @@
       <c r="S89" s="9" t="n"/>
       <c r="T89" s="9" t="n"/>
       <c r="U89" s="9" t="n"/>
-      <c r="V89" s="9" t="n"/>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="8" t="n"/>
@@ -5473,7 +5368,6 @@
       <c r="S90" s="8" t="n"/>
       <c r="T90" s="8" t="n"/>
       <c r="U90" s="8" t="n"/>
-      <c r="V90" s="8" t="n"/>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="9" t="n"/>
@@ -5497,7 +5391,6 @@
       <c r="S91" s="9" t="n"/>
       <c r="T91" s="9" t="n"/>
       <c r="U91" s="9" t="n"/>
-      <c r="V91" s="9" t="n"/>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="8" t="n"/>
@@ -5521,7 +5414,6 @@
       <c r="S92" s="8" t="n"/>
       <c r="T92" s="8" t="n"/>
       <c r="U92" s="8" t="n"/>
-      <c r="V92" s="8" t="n"/>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="9" t="n"/>
@@ -5545,7 +5437,6 @@
       <c r="S93" s="9" t="n"/>
       <c r="T93" s="9" t="n"/>
       <c r="U93" s="9" t="n"/>
-      <c r="V93" s="9" t="n"/>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="8" t="n"/>
@@ -5569,7 +5460,6 @@
       <c r="S94" s="8" t="n"/>
       <c r="T94" s="8" t="n"/>
       <c r="U94" s="8" t="n"/>
-      <c r="V94" s="8" t="n"/>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="9" t="n"/>
@@ -5593,7 +5483,6 @@
       <c r="S95" s="9" t="n"/>
       <c r="T95" s="9" t="n"/>
       <c r="U95" s="9" t="n"/>
-      <c r="V95" s="9" t="n"/>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="8" t="n"/>
@@ -5617,7 +5506,6 @@
       <c r="S96" s="8" t="n"/>
       <c r="T96" s="8" t="n"/>
       <c r="U96" s="8" t="n"/>
-      <c r="V96" s="8" t="n"/>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="9" t="n"/>
@@ -5641,7 +5529,6 @@
       <c r="S97" s="9" t="n"/>
       <c r="T97" s="9" t="n"/>
       <c r="U97" s="9" t="n"/>
-      <c r="V97" s="9" t="n"/>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="8" t="n"/>
@@ -5665,7 +5552,6 @@
       <c r="S98" s="8" t="n"/>
       <c r="T98" s="8" t="n"/>
       <c r="U98" s="8" t="n"/>
-      <c r="V98" s="8" t="n"/>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="9" t="n"/>
@@ -5689,7 +5575,6 @@
       <c r="S99" s="9" t="n"/>
       <c r="T99" s="9" t="n"/>
       <c r="U99" s="9" t="n"/>
-      <c r="V99" s="9" t="n"/>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="8" t="n"/>
@@ -5713,7 +5598,6 @@
       <c r="S100" s="8" t="n"/>
       <c r="T100" s="8" t="n"/>
       <c r="U100" s="8" t="n"/>
-      <c r="V100" s="8" t="n"/>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="9" t="n"/>
@@ -5737,7 +5621,6 @@
       <c r="S101" s="9" t="n"/>
       <c r="T101" s="9" t="n"/>
       <c r="U101" s="9" t="n"/>
-      <c r="V101" s="9" t="n"/>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="A102" s="8" t="n"/>
@@ -5761,7 +5644,6 @@
       <c r="S102" s="8" t="n"/>
       <c r="T102" s="8" t="n"/>
       <c r="U102" s="8" t="n"/>
-      <c r="V102" s="8" t="n"/>
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="9" t="n"/>
@@ -5785,7 +5667,6 @@
       <c r="S103" s="9" t="n"/>
       <c r="T103" s="9" t="n"/>
       <c r="U103" s="9" t="n"/>
-      <c r="V103" s="9" t="n"/>
     </row>
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="8" t="n"/>
@@ -5809,7 +5690,6 @@
       <c r="S104" s="8" t="n"/>
       <c r="T104" s="8" t="n"/>
       <c r="U104" s="8" t="n"/>
-      <c r="V104" s="8" t="n"/>
     </row>
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="9" t="n"/>
@@ -5833,15 +5713,17 @@
       <c r="S105" s="9" t="n"/>
       <c r="T105" s="9" t="n"/>
       <c r="U105" s="9" t="n"/>
-      <c r="V105" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A1:U1"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation sqref="D5:D105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"Class I,Class II,Class III"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J5:J105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+      <formula1>"1,0"</formula1>
     </dataValidation>
     <dataValidation sqref="K5:K105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
@@ -5849,13 +5731,10 @@
     <dataValidation sqref="L5:L105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="O5:O105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="P5:P105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
-      <formula1>"1,0"</formula1>
-    </dataValidation>
-    <dataValidation sqref="R5:R105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="Q5:Q105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"Internal,External,Both"</formula1>
     </dataValidation>
   </dataValidations>

--- a/assetcore/public/import_templates/02_imm00_ncc_model_hopdong_sla.xlsx
+++ b/assetcore/public/import_templates/02_imm00_ncc_model_hopdong_sla.xlsx
@@ -535,8 +535,8 @@
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
@@ -556,7 +556,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📋 HƯỚNG DẪN IMPORT: Nhà cung cấp (Supplier)  |  Điền dữ liệu từ hàng 5 trở xuống. Cột đỏ = bắt buộc. Không xóa hàng 2-4.</t>
+          <t>📋 HƯỚNG DẪN IMPORT: Nhà cung cấp (Supplier)  |  Điền dữ liệu từ HÀNG 6 trở xuống (hàng 5 là ví dụ mẫu, hệ thống bỏ qua). Cột đỏ = bắt buộc. Không xoá/không sửa hàng 1-5. Cột tham chiếu (danh mục, khoa phòng, vị trí, model, nhà cung cấp) điền TÊN, không điền mã.</t>
         </is>
       </c>
     </row>
@@ -665,12 +665,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Loại NCC (*)</t>
+          <t>Nhóm nhà cung cấp (*)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Loại vendor (*)</t>
+          <t>Loại nhà cung cấp (*)</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -757,12 +757,12 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Manufacturer / Distributor / Calibration Lab / Service Provider</t>
+          <t>Nhà sản xuất / Nhà phân phối / Phòng hiệu chuẩn / Dịch vụ.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Manufacturer / Distributor / Calibration Lab / Service</t>
+          <t>Nhà sản xuất / Nhà phân phối / Phòng hiệu chuẩn / Dịch vụ.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Distributor</t>
+          <t>Nhà phân phối</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Distributor</t>
+          <t>Nhà phân phối</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -2933,13 +2933,13 @@
     <mergeCell ref="A1:R1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="C5:C105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
-      <formula1>"Manufacturer,Distributor,Calibration Lab,Service Provider"</formula1>
+    <dataValidation sqref="C6:C105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+      <formula1>"Nhà sản xuất,Nhà phân phối,Phòng hiệu chuẩn,Dịch vụ"</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
-      <formula1>"Manufacturer,Distributor,Calibration Lab,Service"</formula1>
+    <dataValidation sqref="D6:D105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+      <formula1>"Nhà sản xuất,Nhà phân phối,Phòng hiệu chuẩn,Dịch vụ"</formula1>
     </dataValidation>
-    <dataValidation sqref="R5:R105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="R6:R105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2982,7 +2982,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📋 HƯỚNG DẪN IMPORT: Mô hình thiết bị (Device Model)  |  Điền dữ liệu từ hàng 5 trở xuống. Cột đỏ = bắt buộc. Không xóa hàng 2-4.</t>
+          <t>📋 HƯỚNG DẪN IMPORT: Mô hình thiết bị (Device Model)  |  Điền dữ liệu từ HÀNG 6 trở xuống (hàng 5 là ví dụ mẫu, hệ thống bỏ qua). Cột đỏ = bắt buộc. Không xoá/không sửa hàng 1-5. Cột tham chiếu (danh mục, khoa phòng, vị trí, model, nhà cung cấp) điền TÊN, không điền mã.</t>
         </is>
       </c>
     </row>
@@ -3213,12 +3213,12 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Phải khớp với tên trong sheet 'Danh mục tài sản'.</t>
+          <t>Tên danh mục, khớp sheet 'Danh mục tài sản'. Điền TÊN, KHÔNG điền mã hệ thống.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Class I / Class II / Class III (theo QCVN/WHO).</t>
+          <t>Loại I — Rủi ro thấp / Loại II — Rủi ro trung bình / Loại III — Rủi ro cao (theo QCVN/WHO).</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="Q4" s="6" t="inlineStr">
         <is>
-          <t>Internal / External / Both</t>
+          <t>Nội bộ / Bên ngoài / Cả hai.</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Class II</t>
+          <t>Loại II — Rủi ro trung bình</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>Bên ngoài</t>
         </is>
       </c>
       <c r="R5" s="7" t="inlineStr">
@@ -5719,23 +5719,23 @@
     <mergeCell ref="A1:U1"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation sqref="D5:D105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
-      <formula1>"Class I,Class II,Class III"</formula1>
+    <dataValidation sqref="D6:D105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+      <formula1>"Loại I — Rủi ro thấp,Loại II — Rủi ro trung bình,Loại III — Rủi ro cao"</formula1>
     </dataValidation>
-    <dataValidation sqref="J5:J105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="J6:J105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="K5:K105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="K6:K105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="L6:L105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="O5:O105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="O6:O105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q5:Q105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
-      <formula1>"Internal,External,Both"</formula1>
+    <dataValidation sqref="Q6:Q105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+      <formula1>"Nội bộ,Bên ngoài,Cả hai"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5768,7 +5768,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📋 HƯỚNG DẪN IMPORT: Hợp đồng (Service Contract)  |  Điền dữ liệu từ hàng 5 trở xuống. Cột đỏ = bắt buộc. Không xóa hàng 2-4.</t>
+          <t>📋 HƯỚNG DẪN IMPORT: Hợp đồng (Service Contract)  |  Điền dữ liệu từ HÀNG 6 trở xuống (hàng 5 là ví dụ mẫu, hệ thống bỏ qua). Cột đỏ = bắt buộc. Không xoá/không sửa hàng 1-5. Cột tham chiếu (danh mục, khoa phòng, vị trí, model, nhà cung cấp) điền TÊN, không điền mã.</t>
         </is>
       </c>
     </row>
@@ -5909,12 +5909,12 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Tên NCC phải khớp với sheet 'Nhà cung cấp'.</t>
+          <t>Tên nhà cung cấp, khớp sheet 'Nhà cung cấp'. Điền TÊN, KHÔNG điền mã hệ thống.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Preventive Maintenance / Calibration / Repair / Full Service / Warranty Extension</t>
+          <t>Bảo trì định kỳ / Hiệu chuẩn / Sửa chữa / Toàn diện / Gia hạn bảo hành.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Preventive Maintenance</t>
+          <t>Bảo trì định kỳ</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -7421,10 +7421,10 @@
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="D5:D105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
-      <formula1>"Preventive Maintenance,Calibration,Repair,Full Service,Warranty Extension"</formula1>
+    <dataValidation sqref="D6:D105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+      <formula1>"Bảo trì định kỳ,Hiệu chuẩn,Sửa chữa,Toàn diện,Gia hạn bảo hành"</formula1>
     </dataValidation>
-    <dataValidation sqref="J5:J105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="J6:J105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7442,7 +7442,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
@@ -7459,7 +7459,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📋 HƯỚNG DẪN IMPORT: Chính sách SLA  |  Điền dữ liệu từ hàng 5 trở xuống. Cột đỏ = bắt buộc. Không xóa hàng 2-4.</t>
+          <t>📋 HƯỚNG DẪN IMPORT: Chính sách SLA  |  Điền dữ liệu từ HÀNG 6 trở xuống (hàng 5 là ví dụ mẫu, hệ thống bỏ qua). Cột đỏ = bắt buộc. Không xoá/không sửa hàng 1-5. Cột tham chiếu (danh mục, khoa phòng, vị trí, model, nhà cung cấp) điền TÊN, không điền mã.</t>
         </is>
       </c>
     </row>
@@ -7605,7 +7605,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>P1 Critical / P1 High / P2 / P3 / P4</t>
+          <t>P1 — Khẩn cấp / P2 — Cao / P3 — Trung bình / P4 — Thấp.</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Low / Medium / High / Critical — áp dụng cho rủi ro nào.</t>
+          <t>Thấp / Trung bình / Cao / Nghiêm trọng — áp dụng cho mức rủi ro nào.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>P1 Critical</t>
+          <t>P1 — Khẩn cấp</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Nghiêm trọng</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -9232,16 +9232,16 @@
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="B5:B105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
-      <formula1>"P1 Critical,P1 High,P2,P3,P4"</formula1>
+    <dataValidation sqref="B6:B105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+      <formula1>"P1 — Khẩn cấp,P2 — Cao,P3 — Trung bình,P4 — Thấp"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
-      <formula1>"Low,Medium,High,Critical"</formula1>
+    <dataValidation sqref="E6:E105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+      <formula1>"Thấp,Trung bình,Cao,Nghiêm trọng"</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="L6:L105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="M6:M105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>

--- a/assetcore/public/import_templates/02_imm00_ncc_model_hopdong_sla.xlsx
+++ b/assetcore/public/import_templates/02_imm00_ncc_model_hopdong_sla.xlsx
@@ -2933,13 +2933,13 @@
     <mergeCell ref="A1:R1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="C6:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"Nhà sản xuất,Nhà phân phối,Phòng hiệu chuẩn,Dịch vụ"</formula1>
     </dataValidation>
-    <dataValidation sqref="D6:D105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="D6:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"Nhà sản xuất,Nhà phân phối,Phòng hiệu chuẩn,Dịch vụ"</formula1>
     </dataValidation>
-    <dataValidation sqref="R6:R105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="R6:R1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5719,22 +5719,22 @@
     <mergeCell ref="A1:U1"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation sqref="D6:D105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="D6:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"Loại I — Rủi ro thấp,Loại II — Rủi ro trung bình,Loại III — Rủi ro cao"</formula1>
     </dataValidation>
-    <dataValidation sqref="J6:J105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="J6:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="K6:K105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="K6:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="L6:L105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="L6:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="O6:O105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="O6:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q6:Q105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="Q6:Q1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"Nội bộ,Bên ngoài,Cả hai"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7421,10 +7421,10 @@
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="D6:D105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="D6:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"Bảo trì định kỳ,Hiệu chuẩn,Sửa chữa,Toàn diện,Gia hạn bảo hành"</formula1>
     </dataValidation>
-    <dataValidation sqref="J6:J105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="J6:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9232,16 +9232,16 @@
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="B6:B105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="B6:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"P1 — Khẩn cấp,P2 — Cao,P3 — Trung bình,P4 — Thấp"</formula1>
     </dataValidation>
-    <dataValidation sqref="E6:E105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="E6:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"Thấp,Trung bình,Cao,Nghiêm trọng"</formula1>
     </dataValidation>
-    <dataValidation sqref="L6:L105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="L6:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="M6:M105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="M6:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>
